--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, PostgreSQL, MySQL, NoSQL, Tableau, Python</t>
+          <t>Gemini, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c136294cfd98fe</t>
+          <t>https://www.indeed.com/viewjob?jk=88bb92df5ae0e653</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6177a38e86fbab44</t>
+          <t>https://www.indeed.com/viewjob?jk=0942a9a3d6620829</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Associate Power BI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCiM</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, MySQL, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9409f6bf6d0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5ba03d2b8f17d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer Oncology Analytics</t>
+          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a8530ac9c848be</t>
+          <t>https://www.indeed.com/viewjob?jk=be5b7a9627f86c3e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>JAMY INTERACTIVE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Glue, Redshift, Kinesis, Terraform, Snowflake, Redshift, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ca8eea8c20d4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=df016cb07da6d198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Co-Op</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Veracode</t>
+          <t>Unify Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=826dab067cddd761</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer (Info Retrieval)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a91a5c4ac0767566</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Reporting Developer III - Data Scientist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Gulfstream Aerospace</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Savannah, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, LightGBM, AWS SageMaker, MLflow, CI/CD, Databricks, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6c19b8a4e2f6a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Arch Telecom</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e777e1047bb41aa</t>
+          <t>https://www.indeed.com/viewjob?jk=64f1137991d8ec7a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Databricks, Hadoop, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bb92df5ae0e653</t>
+          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform, Kafka, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0942a9a3d6620829</t>
+          <t>https://www.indeed.com/viewjob?jk=8cce8cf60d6f98b4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Power BI Developer</t>
+          <t>AI/ML Engineer - Python / Agentic AI - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, MySQL, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5ba03d2b8f17d</t>
+          <t>https://www.indeed.com/viewjob?jk=c58ae5fb33bddf6d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
+          <t>Sr AI/ML Engineer Remote - Remote in Eastern Time Zone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5b7a9627f86c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=95a5aea5afc870d0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JAMY INTERACTIVE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, Jenkins, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,322 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df016cb07da6d198</t>
+          <t>https://www.indeed.com/viewjob?jk=05a7c1d87b1ffdda</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unify Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=597c8270d2edc913</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Silicon System AI Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PySpark, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80b01181abf49883</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S3, EC2, Glue, Redshift, Kinesis, Terraform, Snowflake, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022f699606afdd8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ed8840ad92bd8c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Scientist 2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64f1137991d8ec7a</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7878e74b8b7c2616</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Scientist 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a0661ffb4e51ca5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Product Security Engineer - Apps</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40a3cca3b1b6be3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>iHeartMedia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Docker, Git, Redshift, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e7ad0521ff70586</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Media and Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Go Fish Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Databricks, Hadoop, PostgreSQL</t>
+          <t>Data Scientist, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e3c201f23e6a22</t>
+          <t>https://www.indeed.com/viewjob?jk=77d676559a3bdbee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Data Scientist - Healthcare Supply Chain Riskdata</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cce8cf60d6f98b4</t>
+          <t>https://www.indeed.com/viewjob?jk=db0eb6d7d0a36f02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Python / Agentic AI - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Data Lake, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c58ae5fb33bddf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer Remote - Remote in Eastern Time Zone</t>
+          <t>Automation Engineer (Entry Level)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95a5aea5afc870d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3ccee5e87bd177</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Engineer / LLM Workflow Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>World Hyundai Matteson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Matteson, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kinesis, Docker, Jenkins, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,322 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a7c1d87b1ffdda</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Gemini, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=597c8270d2edc913</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Silicon System AI Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PySpark, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80b01181abf49883</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>S3, EC2, Glue, Redshift, Kinesis, Terraform, Snowflake, Redshift, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a27a8acf3bc1bc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022f699606afdd8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ed8840ad92bd8c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Scientist 2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7878e74b8b7c2616</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AI Scientist 2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0661ffb4e51ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Product Security Engineer - Apps</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40a3cca3b1b6be3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>iHeartMedia</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Docker, Git, Redshift, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7ad0521ff70586</t>
+          <t>https://www.indeed.com/viewjob?jk=65672f1d356752d4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Media and Marketing Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Go Fish Digital</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, XGBoost, LightGBM, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d676559a3bdbee</t>
+          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist - Healthcare Supply Chain Riskdata</t>
+          <t>AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, Pinecone, Kinesis, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0eb6d7d0a36f02</t>
+          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Data Scientist Computer Vision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, YOLO, AWS SageMaker, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f71870dc0f7bc53</t>
+          <t>https://www.indeed.com/viewjob?jk=10d9db2157c03dce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Automation Engineer (Entry Level)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,532 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3ccee5e87bd177</t>
+          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer / LLM Workflow Developer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>World Hyundai Matteson</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Matteson, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Clickhouse)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bba6ced3ac158918</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr Mgr Data Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Java)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Decatur, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, XGBoost, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e6b1f5666b89f22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mid-Level Engineer, Global</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, Git, Snowflake, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer II Devx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FastAPI, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=286b48fc68f0f56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vantor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd7063553c2206e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Endpoint Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65672f1d356752d4</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05ddbdea63d13817</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab55f0f754b6e4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b3f76cc2b75ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, AKS, CI/CD, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ac508b2ed65290a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Agentic Engineer - Systems</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sunlight Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, AKS, CI/CD, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adbb8d1fa4fcd154</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, XGBoost, LightGBM, MLflow, Docker</t>
+          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Apache Airflow, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10f6b2d0d1b341d</t>
+          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, Pinecone, Kinesis, MLflow, CI/CD</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Databricks, Hadoop, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6fecac436797a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist Computer Vision</t>
+          <t>SAP Procurement AI Architect - Multiple Locations</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, YOLO, AWS SageMaker, MLflow</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d9db2157c03dce</t>
+          <t>https://www.indeed.com/viewjob?jk=2db91087f19eaa4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a32bf71ba33ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=68c57d9099cd3239</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3db28285f41c46</t>
+          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3989068a8778fb79</t>
+          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Microsoft Modern Work Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Citrin Cooperman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, Docker</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba6ced3ac158918</t>
+          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Mgr Data Engineering</t>
+          <t>AI Engineer Intern (Entry-Level) — Custom GPT Bot (LLM / RAG)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MINDFUL TECH SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e707506ab6122a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0778251fc7fb36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338db949c564e874</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b06042264e1b44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, XGBoost, Hadoop, Python</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6b1f5666b89f22</t>
+          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Senior Geospatial Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Data Lake, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e006537abb3ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior Dynatrace Observability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Git, Snowflake, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c5c7e7de56c6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II Devx</t>
+          <t>AI Engineering Intern - Summer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FastAPI, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286b48fc68f0f56e</t>
+          <t>https://www.indeed.com/viewjob?jk=29916cb54e09ea8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BI Solutions Engineer</t>
+          <t>ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>JASCO PRODUCTS COMPANY LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Data Lake, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd7063553c2206e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1271f673d1598e1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Endpoint Engineer</t>
+          <t>Data Engineer, Gen AI, Music</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ddbdea63d13817</t>
+          <t>https://www.indeed.com/viewjob?jk=bc059682612f4138</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab55f0f754b6e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b3f76cc2b75ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, AKS, CI/CD, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,287 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac508b2ed65290a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Agentic Engineer - Systems</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sunlight Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Product Owner</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rolling Meadows, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Native Software Engineer - (100% Remote)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Syncreon Consulting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apex, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, AKS, CI/CD, PostgreSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adbb8d1fa4fcd154</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b917774cceb5a6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Application Development</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08209567d3241c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - AI Machine Learning</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3069e7b50b7a5365</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Apprentice, DevOps and IT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Purchasing Platform</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd846420de59863c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineer I (AWS, Databricks, PySpark)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8252665d677e2200</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UC Davis Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a54814b4523b292</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Associate-Dallas</t>
+          <t>Senior Data Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Apache Airflow, Terraform, Snowflake</t>
+          <t>RAG, Copilot, Cortex, Redshift, BigQuery, Synapse, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452922c279cc36e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Databricks, Hadoop, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a309f4efa98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP Procurement AI Architect - Multiple Locations</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Kafka, Hadoop, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db91087f19eaa4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc89b8593855079</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c57d9099cd3239</t>
+          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Software Engineer (Cloud Storage)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b72bdc255bbf6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb28dc6f53b499fd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NetApp Emerging Talent - Entry Level Software Engineer (Cloud Storage)</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e07865da969c4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=95dffb950b904555</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Modern Work Consultant</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Citrin Cooperman</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Data Lake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d034c0b8905492</t>
+          <t>https://www.indeed.com/viewjob?jk=d51b613f0607e403</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer Intern (Entry-Level) — Custom GPT Bot (LLM / RAG)</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MINDFUL TECH SOLUTIONS</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, CI/CD, Git, Python</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0778251fc7fb36</t>
+          <t>https://www.indeed.com/viewjob?jk=d599d5112a818033</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b06042264e1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=17e7223bea2ee95b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c717630a440c614c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9b9d166fa730e7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Geospatial Solutions Architect</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4968b1c75b8ea91</t>
+          <t>https://www.indeed.com/viewjob?jk=ec97eb644c4d1bbb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Dynatrace Observability Engineer</t>
+          <t>Senior Software Engineer, Backend/Investigative Agent</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504c2eb153af2545</t>
+          <t>https://www.indeed.com/viewjob?jk=1642e66f5c9fe7be</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineering Intern - Summer</t>
+          <t>Azure AI Foundry Architect (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Docker, AKS, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29916cb54e09ea8c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d72c82ae191e5db</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANALYTICS ENGINEER</t>
+          <t>Angular / JAVA Full Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JASCO PRODUCTS COMPANY LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1271f673d1598e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, Gen AI, Music</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc059682612f4138</t>
+          <t>https://www.indeed.com/viewjob?jk=529d89c75b421b52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e84b525a6d6412</t>
+          <t>https://www.indeed.com/viewjob?jk=36dff1c9f95fb7af</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38299c9de7d6d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d773b4d1cf66e1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff045a7655f5a9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ba469aaf06d5d2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d9a99d3fb7e65b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6275722da23771</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33815bde90512ef</t>
+          <t>https://www.indeed.com/viewjob?jk=158b4669376c6316</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Native Software Engineer - (100% Remote)</t>
+          <t>Software Engineer III, Fullstack/Investigative Agent</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Flock</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b917774cceb5a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=255fb76f803f5061</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Application Development</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Databricks, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08209567d3241c23</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAP iXp Intern - AI Machine Learning</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>MachineMetrics, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, R, Scala, A/B Testing</t>
+          <t>Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3069e7b50b7a5365</t>
+          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Apprentice, DevOps and IT</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Purchasing Platform</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd846420de59863c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1cb4583c2488b1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I (AWS, Databricks, PySpark)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, R</t>
+          <t>S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,322 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8252665d677e2200</t>
+          <t>https://www.indeed.com/viewjob?jk=932e972b8897112c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UC Davis Health</t>
+          <t>Kinstead</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab0cbf8436662615</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Workflow Systems</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kinstead</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0c52df5169e8d56</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aveva PI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42dd34631f8a4a3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend Developer TS/SCI with Polygraph</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e295df2c58123c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DATA SCIENTIST III</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Frost</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32da36a8ecfaa9fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Customer Engineer - AI / ML</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a54814b4523b292</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4524138abc94d7b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Confie</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=441946015ddc7663</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Agent Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d0f6c4aed86ff7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data and Analytics Solution Sales Executive - Commercial US West</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784cac9df9842aae</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-14.xlsx
+++ b/daily_matches/job_matches_2026-04-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer 2026 - US,UK</t>
+          <t>Architect I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Redshift, BigQuery, Synapse, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Kinesis, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d01fdc4061dd2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d97da40a8da560</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0467416d94bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=085872f73883326c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Kafka, Hadoop, Matplotlib, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc89b8593855079</t>
+          <t>https://www.indeed.com/viewjob?jk=fa79af047e73dc3e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf17dcf23ea3201f</t>
+          <t>https://www.indeed.com/viewjob?jk=34987f860a590c53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb28dc6f53b499fd</t>
+          <t>https://www.indeed.com/viewjob?jk=62c75d5f8fbde70d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dffb950b904555</t>
+          <t>https://www.indeed.com/viewjob?jk=79f8bdec75d776c6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Rocket Close</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51b613f0607e403</t>
+          <t>https://www.indeed.com/viewjob?jk=9fce91f5c39bd4ed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Machine Learning Engineer, Data Mining</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d599d5112a818033</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8e865013898889</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, PyTorch, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e7223bea2ee95b</t>
+          <t>https://www.indeed.com/viewjob?jk=75bae6cf92be1a44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, PyTorch, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9b9d166fa730e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a78d3c4a127089</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, PyTorch, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec97eb644c4d1bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d314ef92d095ef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend/Investigative Agent</t>
+          <t>Senior Software Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, FastAPI, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1642e66f5c9fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=be067cd831de5cd9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure AI Foundry Architect (Remote)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SecurityScorecard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, AKS, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d72c82ae191e5db</t>
+          <t>https://www.indeed.com/viewjob?jk=b78e7c6ff3638e80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Angular / JAVA Full Stack Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Medeloop</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfd60088aef43d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a81ed0b08e8f07f7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Full-Stack Developer (AWS, TS, React)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>RAG, S3, Glue, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529d89c75b421b52</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3a148287061e68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, NoSQL, Power BI, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36dff1c9f95fb7af</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd9651c7e25101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>Machine Learning Engineer, RAG, Git, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d773b4d1cf66e1</t>
+          <t>https://www.indeed.com/viewjob?jk=77aa3568008eb11c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Customer Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ba469aaf06d5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce76453b543c4f7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Samba TV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>Data Scientist, Git, Databricks, PySpark, Python, R, Scala, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6275722da23771</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce83c20a0ed953e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
+          <t>Data Scientist – Revenue Management</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Flock</t>
+          <t>Arconic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,497 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158b4669376c6316</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer III, Fullstack/Investigative Agent</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Flock</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=255fb76f803f5061</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Empirx Health</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Databricks, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e81f16ad428334</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MachineMetrics, Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80173e5fca484063</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>adonis</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1cb4583c2488b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>adonis</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=932e972b8897112c</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Product Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Kinstead</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0cbf8436662615</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer, Workflow Systems</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Kinstead</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c52df5169e8d56</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Aveva PI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42dd34631f8a4a3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Software Engineer - Backend Developer TS/SCI with Polygraph</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e295df2c58123c</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DATA SCIENTIST III</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Frost</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32da36a8ecfaa9fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Customer Engineer - AI / ML</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4524138abc94d7b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Confie</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Addison, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=441946015ddc7663</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI Agent Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d0f6c4aed86ff7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Data and Analytics Solution Sales Executive - Commercial US West</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Git, Snowflake, Databricks, BigQuery, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=784cac9df9842aae</t>
+          <t>https://www.indeed.com/viewjob?jk=5363ef565c82a4c1</t>
         </is>
       </c>
     </row>
